--- a/outputs/templates/比较法测算_模板.xlsx
+++ b/outputs/templates/比较法测算_模板.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>B6*B7*B8*B9*B10*B11*B12</f>
+        <f>ROUND(B6*B7*B8*B9*B10*B11*B12,0)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>C6*C7*C8*C9*C10*C11*C12</f>
+        <f>ROUND(C6*C7*C8*C9*C10*C11*C12,0)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>D6*D7*D8*D9*D10*D11*D12</f>
+        <f>ROUND(D6*D7*D8*D9*D10*D11*D12,0)</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>E6*E7*E8*E9*E10*E11*E12</f>
+        <f>ROUND(E6*E7*E8*E9*E10*E11*E12,0)</f>
         <v/>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B4" s="9">
-        <f>AVERAGE(可比实例数据!B13:E13)</f>
+        <f>ROUND(AVERAGE(可比实例数据!B13:E13),0)</f>
         <v/>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>SUMPRODUCT(可比实例数据!B13:E13*{1,1,1,1})/SUMPRODUCT({1,1,1,1})</f>
+        <f>ROUND(SUMPRODUCT(可比实例数据!B13:E13*{1,1,1,1})/SUMPRODUCT({1,1,1,1}),0)</f>
         <v/>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>MEDIAN(可比实例数据!B13:E13)</f>
+        <f>ROUND(MEDIAN(可比实例数据!B13:E13),0)</f>
         <v/>
       </c>
       <c r="C6" s="14" t="inlineStr">

--- a/outputs/templates/比较法测算_模板.xlsx
+++ b/outputs/templates/比较法测算_模板.xlsx
@@ -716,10 +716,8 @@
           <t>成交价格 (元/m²)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>如: 25000</t>
-        </is>
+      <c r="B6" s="7" t="n">
+        <v>25000</v>
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
@@ -736,10 +734,8 @@
           <t>标准化调整系数</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
@@ -756,10 +752,8 @@
           <t>交易情况修正系数</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
@@ -776,10 +770,8 @@
           <t>市场状况调整系数</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B9" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
@@ -796,10 +788,8 @@
           <t>区位状况调整系数</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B10" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
@@ -816,10 +806,8 @@
           <t>实物状况调整系数</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B11" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
@@ -836,10 +824,8 @@
           <t>权益状况调整系数</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="B12" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>

--- a/outputs/templates/比较法测算_模板.xlsx
+++ b/outputs/templates/比较法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可比实例数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="比较价值汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="可比实例数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="比较价值汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/templates/比较法测算_模板.xlsx
+++ b/outputs/templates/比较法测算_模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="可比实例数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="比较价值汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可比实例数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="比较价值汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
